--- a/finance/_refresh_gojek.xlsx
+++ b/finance/_refresh_gojek.xlsx
@@ -45,8 +45,8 @@
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$5</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$52</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$52</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$42</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1949,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8065,23 +8065,23 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>Mandalika Marina Zone → Kuta Lombok main beach</t>
+          <t>East Coast → Marina Bay</t>
         </is>
       </c>
       <c r="D33" s="31" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>15.32</v>
+        <v>18</v>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G33" s="32" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H33" s="19" t="n">
@@ -8096,7 +8096,7 @@
         <v/>
       </c>
       <c r="K33" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J33,1))</f>
+        <f>MIN(24,FLOOR(60*service_hr/J33,1))</f>
         <v/>
       </c>
       <c r="L33" s="34">
@@ -8184,20 +8184,12 @@
         <v/>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI33" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>111000</v>
+      </c>
+      <c r="AH33" s="32" t="n"/>
+      <c r="AI33" s="32" t="n"/>
       <c r="AJ33" s="39" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AK33" s="34">
         <f>IF(AG33="","",AG33*AJ33)</f>
@@ -8222,7 +8214,7 @@
       <c r="AP33" s="40" t="n"/>
       <c r="AQ33" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR33" s="41" t="n"/>
@@ -8242,14 +8234,10 @@
       </c>
       <c r="AX33" s="44" t="inlineStr">
         <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY33" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
+          <t>NO commuter ferry exists East Coast-&gt;Marina/CBD — road commute only (ECP). Singapore River taxi (Marina&lt;-&gt;Robertson Quay) is intra-river at S$3-7 (commuter single-class, no premium tier; R5-EXT). Harbour water-taxi is whole-boat charter S$80-130/trip (overclaim). Modeled premium per-seat commute fare anchored at road/Grab parity East Coast-&gt;CBD ~S$24 = ~$18.</t>
+        </is>
+      </c>
+      <c r="AY33" s="44" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
@@ -8264,14 +8252,14 @@
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>Bangsal Harbour → Gili Air main jetty</t>
+          <t>Singapore → Batam (Harbour Bay / Nongsa)</t>
         </is>
       </c>
       <c r="D34" s="31" t="n">
-        <v>2.1</v>
+        <v>13</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>15.88</v>
+        <v>57</v>
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
@@ -8280,7 +8268,7 @@
       </c>
       <c r="G34" s="32" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>med-high</t>
         </is>
       </c>
       <c r="H34" s="19" t="n">
@@ -8383,20 +8371,12 @@
         <v/>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI34" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>350000</v>
+      </c>
+      <c r="AH34" s="32" t="n"/>
+      <c r="AI34" s="32" t="n"/>
       <c r="AJ34" s="39" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AK34" s="34">
         <f>IF(AG34="","",AG34*AJ34)</f>
@@ -8421,7 +8401,7 @@
       <c r="AP34" s="40" t="n"/>
       <c r="AQ34" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR34" s="41" t="n"/>
@@ -8441,14 +8421,10 @@
       </c>
       <c r="AX34" s="44" t="inlineStr">
         <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY34" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
+          <t>Fare ladder Singapore↔Batam: budget SGD28 (Sindo, HarbourFront→Batam Centre); standard SGD40-43 (BatamFast/Majestic, Batam Centre/Harbour Bay); PREMIUM resort-transfer SGD~73 (BatamFast Tanah Merah→Nongsapura serving Nongsa premium resort zone: Montigo, Turi Beach — real bookings Lemon8 ~SGD73, Rome2Rio Rp430k-650k, DirectFerries from SGD33-35).</t>
+        </is>
+      </c>
+      <c r="AY34" s="44" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
@@ -8463,23 +8439,23 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>Marina Bay Cruise Centre Singapore (MBCCS) → ONE°15 Marina Sentosa Cove</t>
+          <t>Marina Bay → Changi Point / Pulau Ubin</t>
         </is>
       </c>
       <c r="D35" s="31" t="n">
-        <v>2.5</v>
+        <v>14.2</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="G35" s="32" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H35" s="19" t="n">
@@ -8582,20 +8558,12 @@
         <v/>
       </c>
       <c r="AG35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI35" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>30000</v>
+      </c>
+      <c r="AH35" s="32" t="n"/>
+      <c r="AI35" s="32" t="n"/>
       <c r="AJ35" s="39" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AK35" s="34">
         <f>IF(AG35="","",AG35*AJ35)</f>
@@ -8620,7 +8588,7 @@
       <c r="AP35" s="40" t="n"/>
       <c r="AQ35" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR35" s="41" t="n"/>
@@ -8640,14 +8608,10 @@
       </c>
       <c r="AX35" s="44" t="inlineStr">
         <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY35" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
+          <t>Only existing boat is the Changi Point-&gt;Pulau Ubin bumboat: S$4/pax one-way (NParks official, T1) — budget single-class, no premium tier. No direct Marina Bay-&gt;Changi/Ubin boat (14nm long leg is greenfield). Private Ubin boat tours/charters $91-297/group = whole-boat (overclaim). Modeled premium per-seat one-way for the 14nm Marina Bay hop ~$28 (above bumboat budget, below charter).</t>
+        </is>
+      </c>
+      <c r="AY35" s="44" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
@@ -8662,23 +8626,23 @@
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>Tigaraja Port (Parapat) → Tomok pier (Samosir)</t>
+          <t>Singapore → Bintan (Lagoi resort zone)</t>
         </is>
       </c>
       <c r="D36" s="31" t="n">
-        <v>3.2</v>
+        <v>21.9</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>18.96</v>
+        <v>69</v>
       </c>
       <c r="F36" s="32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="G36" s="32" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H36" s="19" t="n">
@@ -8781,20 +8745,12 @@
         <v/>
       </c>
       <c r="AG36" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI36" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+        <v>150000</v>
+      </c>
+      <c r="AH36" s="32" t="n"/>
+      <c r="AI36" s="32" t="n"/>
       <c r="AJ36" s="39" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AK36" s="34">
         <f>IF(AG36="","",AG36*AJ36)</f>
@@ -8819,7 +8775,7 @@
       <c r="AP36" s="40" t="n"/>
       <c r="AQ36" s="32" t="inlineStr">
         <is>
-          <t>Estimated</t>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR36" s="41" t="n"/>
@@ -8839,2102 +8795,168 @@
       </c>
       <c r="AX36" s="44" t="inlineStr">
         <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY36" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
+          <t>Bintan Resort Ferries (BRF, official) Tanah Merah↔Bandar Bentan Telani (Lagoi resort zone), fares eff. 12 Mar 2026: Economy one-way SGD62 adult; EMERALD CLASS one-way SGD89 adult (premium per-seat tier, incl levies). 3rd-party budget listings from SGD53. Charter = 180-270 pax whole vessel (excluded, R1).</t>
+        </is>
+      </c>
+      <c r="AY36" s="44" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="45" t="inlineStr">
+        <is>
+          <t>TOTAL / median</t>
+        </is>
+      </c>
+      <c r="T37" s="46">
+        <f>SUM(T4:T36)</f>
+        <v/>
+      </c>
+      <c r="AC37" s="46">
+        <f>SUM(AC4:AC36)</f>
+        <v/>
+      </c>
+      <c r="AD37" s="47">
+        <f>IF(T37=0,"",AC37/T37)</f>
+        <v/>
+      </c>
+      <c r="AL37" s="48">
+        <f>SUM(AL4:AL36)</f>
+        <v/>
+      </c>
+      <c r="AM37" s="46">
+        <f>SUM(AM4:AM36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>Fleet basis</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>Raw vessels (sum)</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>Fleet (rounded once)</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>Market rev/yr (raw sum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>Gojek</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>Singapore → ONE°15 Marina Sentosa Cove</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E37" s="26" t="n">
-        <v>20.36</v>
-      </c>
-      <c r="F37" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G37" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" s="33">
-        <f>60*D37/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J37" s="33">
-        <f>I37+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K37" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J37,1))</f>
-        <v/>
-      </c>
-      <c r="L37" s="34">
-        <f>ROUND(365*mech_uptime*H37,0)</f>
-        <v/>
-      </c>
-      <c r="M37" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N37" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O37" s="34">
-        <f>ROUND(K37*L37*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P37" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q37" s="36">
-        <f>pax_cap*P37</f>
-        <v/>
-      </c>
-      <c r="R37" s="34">
-        <f>Q37*O37</f>
-        <v/>
-      </c>
-      <c r="S37" s="37">
-        <f>E37*discount</f>
-        <v/>
-      </c>
-      <c r="T37" s="38">
-        <f>S37*R37</f>
-        <v/>
-      </c>
-      <c r="U37" s="38">
-        <f>(battery/range_nm)*D37*O37*VLOOKUP(B37,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V37" s="38">
-        <f>VLOOKUP(B37,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W37" s="38">
-        <f>VLOOKUP(B37,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X37" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y37" s="38">
-        <f>VLOOKUP(B37,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z37" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA37" s="38">
-        <f>U37+V37+W37+X37+Y37+Z37</f>
-        <v/>
-      </c>
-      <c r="AB37" s="38">
-        <f>VLOOKUP(B37,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC37" s="38">
-        <f>T37-AA37</f>
-        <v/>
-      </c>
-      <c r="AD37" s="35">
-        <f>IF(T37=0,"",AC37/T37)</f>
-        <v/>
-      </c>
-      <c r="AE37" s="36">
-        <f>IF(AC37&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/AC37)</f>
-        <v/>
-      </c>
-      <c r="AF37" s="33">
-        <f>((D37*O37/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D37*O37*VLOOKUP(B37,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI37" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ37" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK37" s="34">
-        <f>IF(AG37="","",AG37*AJ37)</f>
-        <v/>
-      </c>
-      <c r="AL37" s="34">
-        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AT37="",9.9E+99,AT37),FLOOR(AK37/R37,1)))</f>
-        <v/>
-      </c>
-      <c r="AM37" s="38">
-        <f>IF(AL37="","",AL37*T37)</f>
-        <v/>
-      </c>
-      <c r="AN37" s="36">
-        <f>IF(OR(AG37="",R37=0),"",MIN(IF(AT37="",9.9E+99,AT37),AK37/R37))</f>
-        <v/>
-      </c>
-      <c r="AO37" s="38">
-        <f>IF(AN37="","",AN37*T37)</f>
-        <v/>
-      </c>
-      <c r="AP37" s="40" t="n"/>
-      <c r="AQ37" s="32" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="AR37" s="41" t="n"/>
-      <c r="AS37" s="41" t="n"/>
-      <c r="AT37" s="42" t="n"/>
-      <c r="AU37" s="43">
-        <f>IF(((S37*pax_cap*load_thin*ROUND(K37*L37*revleg_thin,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_thin,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_thin*ROUND(K37*L37*revleg_thin,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_thin,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
-        <v/>
-      </c>
-      <c r="AV37" s="43">
-        <f>IF(((S37*pax_cap*load_mid*ROUND(K37*L37*revleg_mid,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_mid,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_mid*ROUND(K37*L37*revleg_mid,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_mid,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
-        <v/>
-      </c>
-      <c r="AW37" s="43">
-        <f>IF(((S37*pax_cap*load_full*ROUND(K37*L37*revleg_full,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_full,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37))&lt;=0,"",VLOOKUP(B37,country_opex,7,FALSE)/((S37*pax_cap*load_full*ROUND(K37*L37*revleg_full,0))-(((battery/range_nm)*D37*ROUND(K37*L37*revleg_full,0)*VLOOKUP(B37,country_opex,3,FALSE))+V37+W37+X37+Y37+Z37)))</f>
-        <v/>
-      </c>
-      <c r="AX37" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY37" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B38" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C38" s="30" t="inlineStr">
-        <is>
-          <t>East Coast → Marina Bay</t>
-        </is>
-      </c>
-      <c r="D38" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E38" s="26" t="n">
-        <v>18</v>
-      </c>
-      <c r="F38" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="G38" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" s="33">
-        <f>60*D38/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J38" s="33">
-        <f>I38+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K38" s="34">
-        <f>MIN(24,FLOOR(60*service_hr/J38,1))</f>
-        <v/>
-      </c>
-      <c r="L38" s="34">
-        <f>ROUND(365*mech_uptime*H38,0)</f>
-        <v/>
-      </c>
-      <c r="M38" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N38" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O38" s="34">
-        <f>ROUND(K38*L38*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P38" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q38" s="36">
-        <f>pax_cap*P38</f>
-        <v/>
-      </c>
-      <c r="R38" s="34">
-        <f>Q38*O38</f>
-        <v/>
-      </c>
-      <c r="S38" s="37">
-        <f>E38*discount</f>
-        <v/>
-      </c>
-      <c r="T38" s="38">
-        <f>S38*R38</f>
-        <v/>
-      </c>
-      <c r="U38" s="38">
-        <f>(battery/range_nm)*D38*O38*VLOOKUP(B38,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V38" s="38">
-        <f>VLOOKUP(B38,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W38" s="38">
-        <f>VLOOKUP(B38,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X38" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y38" s="38">
-        <f>VLOOKUP(B38,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z38" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA38" s="38">
-        <f>U38+V38+W38+X38+Y38+Z38</f>
-        <v/>
-      </c>
-      <c r="AB38" s="38">
-        <f>VLOOKUP(B38,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC38" s="38">
-        <f>T38-AA38</f>
-        <v/>
-      </c>
-      <c r="AD38" s="35">
-        <f>IF(T38=0,"",AC38/T38)</f>
-        <v/>
-      </c>
-      <c r="AE38" s="36">
-        <f>IF(AC38&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/AC38)</f>
-        <v/>
-      </c>
-      <c r="AF38" s="33">
-        <f>((D38*O38/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D38*O38*VLOOKUP(B38,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG38" s="31" t="n">
-        <v>111000</v>
-      </c>
-      <c r="AH38" s="32" t="n"/>
-      <c r="AI38" s="32" t="n"/>
-      <c r="AJ38" s="39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK38" s="34">
-        <f>IF(AG38="","",AG38*AJ38)</f>
-        <v/>
-      </c>
-      <c r="AL38" s="34">
-        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AT38="",9.9E+99,AT38),FLOOR(AK38/R38,1)))</f>
-        <v/>
-      </c>
-      <c r="AM38" s="38">
-        <f>IF(AL38="","",AL38*T38)</f>
-        <v/>
-      </c>
-      <c r="AN38" s="36">
-        <f>IF(OR(AG38="",R38=0),"",MIN(IF(AT38="",9.9E+99,AT38),AK38/R38))</f>
-        <v/>
-      </c>
-      <c r="AO38" s="38">
-        <f>IF(AN38="","",AN38*T38)</f>
-        <v/>
-      </c>
-      <c r="AP38" s="40" t="n"/>
-      <c r="AQ38" s="32" t="inlineStr">
-        <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="AR38" s="41" t="n"/>
-      <c r="AS38" s="41" t="n"/>
-      <c r="AT38" s="42" t="n"/>
-      <c r="AU38" s="43">
-        <f>IF(((S38*pax_cap*load_thin*ROUND(K38*L38*revleg_thin,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_thin,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_thin*ROUND(K38*L38*revleg_thin,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_thin,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
-        <v/>
-      </c>
-      <c r="AV38" s="43">
-        <f>IF(((S38*pax_cap*load_mid*ROUND(K38*L38*revleg_mid,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_mid,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_mid*ROUND(K38*L38*revleg_mid,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_mid,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
-        <v/>
-      </c>
-      <c r="AW38" s="43">
-        <f>IF(((S38*pax_cap*load_full*ROUND(K38*L38*revleg_full,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_full,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38))&lt;=0,"",VLOOKUP(B38,country_opex,7,FALSE)/((S38*pax_cap*load_full*ROUND(K38*L38*revleg_full,0))-(((battery/range_nm)*D38*ROUND(K38*L38*revleg_full,0)*VLOOKUP(B38,country_opex,3,FALSE))+V38+W38+X38+Y38+Z38)))</f>
-        <v/>
-      </c>
-      <c r="AX38" s="44" t="inlineStr">
-        <is>
-          <t>NO commuter ferry exists East Coast-&gt;Marina/CBD — road commute only (ECP). Singapore River taxi (Marina&lt;-&gt;Robertson Quay) is intra-river at S$3-7 (commuter single-class, no premium tier; R5-EXT). Harbour water-taxi is whole-boat charter S$80-130/trip (overclaim). Modeled premium per-seat commute fare anchored at road/Grab parity East Coast-&gt;CBD ~S$24 = ~$18.</t>
-        </is>
-      </c>
-      <c r="AY38" s="44" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B39" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>Tuktuk Siadong village pier → Ambarita</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="E39" s="26" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="F39" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G39" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="H39" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="33">
-        <f>60*D39/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J39" s="33">
-        <f>I39+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K39" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J39,1))</f>
-        <v/>
-      </c>
-      <c r="L39" s="34">
-        <f>ROUND(365*mech_uptime*H39,0)</f>
-        <v/>
-      </c>
-      <c r="M39" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N39" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O39" s="34">
-        <f>ROUND(K39*L39*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P39" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q39" s="36">
-        <f>pax_cap*P39</f>
-        <v/>
-      </c>
-      <c r="R39" s="34">
-        <f>Q39*O39</f>
-        <v/>
-      </c>
-      <c r="S39" s="37">
-        <f>E39*discount</f>
-        <v/>
-      </c>
-      <c r="T39" s="38">
-        <f>S39*R39</f>
-        <v/>
-      </c>
-      <c r="U39" s="38">
-        <f>(battery/range_nm)*D39*O39*VLOOKUP(B39,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V39" s="38">
-        <f>VLOOKUP(B39,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W39" s="38">
-        <f>VLOOKUP(B39,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X39" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y39" s="38">
-        <f>VLOOKUP(B39,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z39" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA39" s="38">
-        <f>U39+V39+W39+X39+Y39+Z39</f>
-        <v/>
-      </c>
-      <c r="AB39" s="38">
-        <f>VLOOKUP(B39,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC39" s="38">
-        <f>T39-AA39</f>
-        <v/>
-      </c>
-      <c r="AD39" s="35">
-        <f>IF(T39=0,"",AC39/T39)</f>
-        <v/>
-      </c>
-      <c r="AE39" s="36">
-        <f>IF(AC39&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/AC39)</f>
-        <v/>
-      </c>
-      <c r="AF39" s="33">
-        <f>((D39*O39/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D39*O39*VLOOKUP(B39,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG39" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI39" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ39" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK39" s="34">
-        <f>IF(AG39="","",AG39*AJ39)</f>
-        <v/>
-      </c>
-      <c r="AL39" s="34">
-        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AT39="",9.9E+99,AT39),FLOOR(AK39/R39,1)))</f>
-        <v/>
-      </c>
-      <c r="AM39" s="38">
-        <f>IF(AL39="","",AL39*T39)</f>
-        <v/>
-      </c>
-      <c r="AN39" s="36">
-        <f>IF(OR(AG39="",R39=0),"",MIN(IF(AT39="",9.9E+99,AT39),AK39/R39))</f>
-        <v/>
-      </c>
-      <c r="AO39" s="38">
-        <f>IF(AN39="","",AN39*T39)</f>
-        <v/>
-      </c>
-      <c r="AP39" s="40" t="n"/>
-      <c r="AQ39" s="32" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="AR39" s="41" t="n"/>
-      <c r="AS39" s="41" t="n"/>
-      <c r="AT39" s="42" t="n"/>
-      <c r="AU39" s="43">
-        <f>IF(((S39*pax_cap*load_thin*ROUND(K39*L39*revleg_thin,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_thin,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_thin*ROUND(K39*L39*revleg_thin,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_thin,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
-        <v/>
-      </c>
-      <c r="AV39" s="43">
-        <f>IF(((S39*pax_cap*load_mid*ROUND(K39*L39*revleg_mid,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_mid,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_mid*ROUND(K39*L39*revleg_mid,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_mid,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
-        <v/>
-      </c>
-      <c r="AW39" s="43">
-        <f>IF(((S39*pax_cap*load_full*ROUND(K39*L39*revleg_full,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_full,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39))&lt;=0,"",VLOOKUP(B39,country_opex,7,FALSE)/((S39*pax_cap*load_full*ROUND(K39*L39*revleg_full,0))-(((battery/range_nm)*D39*ROUND(K39*L39*revleg_full,0)*VLOOKUP(B39,country_opex,3,FALSE))+V39+W39+X39+Y39+Z39)))</f>
-        <v/>
-      </c>
-      <c r="AX39" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY39" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B40" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C40" s="30" t="inlineStr">
-        <is>
-          <t>Marina Bay Cruise Centre Singapore (MBCCS) → Republic of Singapore Yacht Club (RSYC)</t>
-        </is>
-      </c>
-      <c r="D40" s="31" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E40" s="26" t="n">
-        <v>34.36</v>
-      </c>
-      <c r="F40" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G40" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" s="33">
-        <f>60*D40/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J40" s="33">
-        <f>I40+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K40" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J40,1))</f>
-        <v/>
-      </c>
-      <c r="L40" s="34">
-        <f>ROUND(365*mech_uptime*H40,0)</f>
-        <v/>
-      </c>
-      <c r="M40" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N40" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O40" s="34">
-        <f>ROUND(K40*L40*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P40" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q40" s="36">
-        <f>pax_cap*P40</f>
-        <v/>
-      </c>
-      <c r="R40" s="34">
-        <f>Q40*O40</f>
-        <v/>
-      </c>
-      <c r="S40" s="37">
-        <f>E40*discount</f>
-        <v/>
-      </c>
-      <c r="T40" s="38">
-        <f>S40*R40</f>
-        <v/>
-      </c>
-      <c r="U40" s="38">
-        <f>(battery/range_nm)*D40*O40*VLOOKUP(B40,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V40" s="38">
-        <f>VLOOKUP(B40,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W40" s="38">
-        <f>VLOOKUP(B40,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X40" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y40" s="38">
-        <f>VLOOKUP(B40,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z40" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA40" s="38">
-        <f>U40+V40+W40+X40+Y40+Z40</f>
-        <v/>
-      </c>
-      <c r="AB40" s="38">
-        <f>VLOOKUP(B40,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC40" s="38">
-        <f>T40-AA40</f>
-        <v/>
-      </c>
-      <c r="AD40" s="35">
-        <f>IF(T40=0,"",AC40/T40)</f>
-        <v/>
-      </c>
-      <c r="AE40" s="36">
-        <f>IF(AC40&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/AC40)</f>
-        <v/>
-      </c>
-      <c r="AF40" s="33">
-        <f>((D40*O40/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D40*O40*VLOOKUP(B40,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG40" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI40" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ40" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK40" s="34">
-        <f>IF(AG40="","",AG40*AJ40)</f>
-        <v/>
-      </c>
-      <c r="AL40" s="34">
-        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AT40="",9.9E+99,AT40),FLOOR(AK40/R40,1)))</f>
-        <v/>
-      </c>
-      <c r="AM40" s="38">
-        <f>IF(AL40="","",AL40*T40)</f>
-        <v/>
-      </c>
-      <c r="AN40" s="36">
-        <f>IF(OR(AG40="",R40=0),"",MIN(IF(AT40="",9.9E+99,AT40),AK40/R40))</f>
-        <v/>
-      </c>
-      <c r="AO40" s="38">
-        <f>IF(AN40="","",AN40*T40)</f>
-        <v/>
-      </c>
-      <c r="AP40" s="40" t="n"/>
-      <c r="AQ40" s="32" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="AR40" s="41" t="n"/>
-      <c r="AS40" s="41" t="n"/>
-      <c r="AT40" s="42" t="n"/>
-      <c r="AU40" s="43">
-        <f>IF(((S40*pax_cap*load_thin*ROUND(K40*L40*revleg_thin,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_thin,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_thin*ROUND(K40*L40*revleg_thin,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_thin,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
-        <v/>
-      </c>
-      <c r="AV40" s="43">
-        <f>IF(((S40*pax_cap*load_mid*ROUND(K40*L40*revleg_mid,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_mid,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_mid*ROUND(K40*L40*revleg_mid,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_mid,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
-        <v/>
-      </c>
-      <c r="AW40" s="43">
-        <f>IF(((S40*pax_cap*load_full*ROUND(K40*L40*revleg_full,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_full,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40))&lt;=0,"",VLOOKUP(B40,country_opex,7,FALSE)/((S40*pax_cap*load_full*ROUND(K40*L40*revleg_full,0))-(((battery/range_nm)*D40*ROUND(K40*L40*revleg_full,0)*VLOOKUP(B40,country_opex,3,FALSE))+V40+W40+X40+Y40+Z40)))</f>
-        <v/>
-      </c>
-      <c r="AX40" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY40" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B41" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C41" s="30" t="inlineStr">
-        <is>
-          <t>Singapore → Batam (Harbour Bay / Nongsa)</t>
-        </is>
-      </c>
-      <c r="D41" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="E41" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="F41" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G41" s="32" t="inlineStr">
-        <is>
-          <t>med-high</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="33">
-        <f>60*D41/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J41" s="33">
-        <f>I41+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K41" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J41,1))</f>
-        <v/>
-      </c>
-      <c r="L41" s="34">
-        <f>ROUND(365*mech_uptime*H41,0)</f>
-        <v/>
-      </c>
-      <c r="M41" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N41" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O41" s="34">
-        <f>ROUND(K41*L41*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P41" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q41" s="36">
-        <f>pax_cap*P41</f>
-        <v/>
-      </c>
-      <c r="R41" s="34">
-        <f>Q41*O41</f>
-        <v/>
-      </c>
-      <c r="S41" s="37">
-        <f>E41*discount</f>
-        <v/>
-      </c>
-      <c r="T41" s="38">
-        <f>S41*R41</f>
-        <v/>
-      </c>
-      <c r="U41" s="38">
-        <f>(battery/range_nm)*D41*O41*VLOOKUP(B41,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V41" s="38">
-        <f>VLOOKUP(B41,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W41" s="38">
-        <f>VLOOKUP(B41,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X41" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y41" s="38">
-        <f>VLOOKUP(B41,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z41" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA41" s="38">
-        <f>U41+V41+W41+X41+Y41+Z41</f>
-        <v/>
-      </c>
-      <c r="AB41" s="38">
-        <f>VLOOKUP(B41,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC41" s="38">
-        <f>T41-AA41</f>
-        <v/>
-      </c>
-      <c r="AD41" s="35">
-        <f>IF(T41=0,"",AC41/T41)</f>
-        <v/>
-      </c>
-      <c r="AE41" s="36">
-        <f>IF(AC41&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/AC41)</f>
-        <v/>
-      </c>
-      <c r="AF41" s="33">
-        <f>((D41*O41/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D41*O41*VLOOKUP(B41,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG41" s="31" t="n">
-        <v>350000</v>
-      </c>
-      <c r="AH41" s="32" t="n"/>
-      <c r="AI41" s="32" t="n"/>
-      <c r="AJ41" s="39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK41" s="34">
-        <f>IF(AG41="","",AG41*AJ41)</f>
-        <v/>
-      </c>
-      <c r="AL41" s="34">
-        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AT41="",9.9E+99,AT41),FLOOR(AK41/R41,1)))</f>
-        <v/>
-      </c>
-      <c r="AM41" s="38">
-        <f>IF(AL41="","",AL41*T41)</f>
-        <v/>
-      </c>
-      <c r="AN41" s="36">
-        <f>IF(OR(AG41="",R41=0),"",MIN(IF(AT41="",9.9E+99,AT41),AK41/R41))</f>
-        <v/>
-      </c>
-      <c r="AO41" s="38">
-        <f>IF(AN41="","",AN41*T41)</f>
-        <v/>
-      </c>
-      <c r="AP41" s="40" t="n"/>
-      <c r="AQ41" s="32" t="inlineStr">
-        <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="AR41" s="41" t="n"/>
-      <c r="AS41" s="41" t="n"/>
-      <c r="AT41" s="42" t="n"/>
-      <c r="AU41" s="43">
-        <f>IF(((S41*pax_cap*load_thin*ROUND(K41*L41*revleg_thin,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_thin,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_thin*ROUND(K41*L41*revleg_thin,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_thin,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
-        <v/>
-      </c>
-      <c r="AV41" s="43">
-        <f>IF(((S41*pax_cap*load_mid*ROUND(K41*L41*revleg_mid,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_mid,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_mid*ROUND(K41*L41*revleg_mid,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_mid,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
-        <v/>
-      </c>
-      <c r="AW41" s="43">
-        <f>IF(((S41*pax_cap*load_full*ROUND(K41*L41*revleg_full,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_full,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41))&lt;=0,"",VLOOKUP(B41,country_opex,7,FALSE)/((S41*pax_cap*load_full*ROUND(K41*L41*revleg_full,0))-(((battery/range_nm)*D41*ROUND(K41*L41*revleg_full,0)*VLOOKUP(B41,country_opex,3,FALSE))+V41+W41+X41+Y41+Z41)))</f>
-        <v/>
-      </c>
-      <c r="AX41" s="44" t="inlineStr">
-        <is>
-          <t>Fare ladder Singapore↔Batam: budget SGD28 (Sindo, HarbourFront→Batam Centre); standard SGD40-43 (BatamFast/Majestic, Batam Centre/Harbour Bay); PREMIUM resort-transfer SGD~73 (BatamFast Tanah Merah→Nongsapura serving Nongsa premium resort zone: Montigo, Turi Beach — real bookings Lemon8 ~SGD73, Rome2Rio Rp430k-650k, DirectFerries from SGD33-35).</t>
-        </is>
-      </c>
-      <c r="AY41" s="44" t="n"/>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>network_sum / ceil</t>
+        </is>
+      </c>
+      <c r="C41" s="23">
+        <f>SUMIFS(AN4:AN36,A4:A36,"Gojek",AP4:AP36,"=",AQ4:AQ36,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="D41" s="49">
+        <f>IF(C41=0,0,CEILING(C41,1))</f>
+        <v/>
+      </c>
+      <c r="E41" s="50">
+        <f>SUMIFS(AO4:AO36,A4:A36,"Gojek",AP4:AP36,"=",AQ4:AQ36,"Grounded")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B42" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C42" s="30" t="inlineStr">
-        <is>
-          <t>Marina Bay → Changi Point / Pulau Ubin</t>
-        </is>
-      </c>
-      <c r="D42" s="31" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="E42" s="26" t="n">
-        <v>28</v>
-      </c>
-      <c r="F42" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="G42" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="33">
-        <f>60*D42/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J42" s="33">
-        <f>I42+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K42" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J42,1))</f>
-        <v/>
-      </c>
-      <c r="L42" s="34">
-        <f>ROUND(365*mech_uptime*H42,0)</f>
-        <v/>
-      </c>
-      <c r="M42" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N42" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O42" s="34">
-        <f>ROUND(K42*L42*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P42" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q42" s="36">
-        <f>pax_cap*P42</f>
-        <v/>
-      </c>
-      <c r="R42" s="34">
-        <f>Q42*O42</f>
-        <v/>
-      </c>
-      <c r="S42" s="37">
-        <f>E42*discount</f>
-        <v/>
-      </c>
-      <c r="T42" s="38">
-        <f>S42*R42</f>
-        <v/>
-      </c>
-      <c r="U42" s="38">
-        <f>(battery/range_nm)*D42*O42*VLOOKUP(B42,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V42" s="38">
-        <f>VLOOKUP(B42,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W42" s="38">
-        <f>VLOOKUP(B42,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X42" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y42" s="38">
-        <f>VLOOKUP(B42,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z42" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA42" s="38">
-        <f>U42+V42+W42+X42+Y42+Z42</f>
-        <v/>
-      </c>
-      <c r="AB42" s="38">
-        <f>VLOOKUP(B42,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC42" s="38">
-        <f>T42-AA42</f>
-        <v/>
-      </c>
-      <c r="AD42" s="35">
-        <f>IF(T42=0,"",AC42/T42)</f>
-        <v/>
-      </c>
-      <c r="AE42" s="36">
-        <f>IF(AC42&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/AC42)</f>
-        <v/>
-      </c>
-      <c r="AF42" s="33">
-        <f>((D42*O42/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D42*O42*VLOOKUP(B42,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG42" s="31" t="n">
-        <v>30000</v>
-      </c>
-      <c r="AH42" s="32" t="n"/>
-      <c r="AI42" s="32" t="n"/>
-      <c r="AJ42" s="39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK42" s="34">
-        <f>IF(AG42="","",AG42*AJ42)</f>
-        <v/>
-      </c>
-      <c r="AL42" s="34">
-        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AT42="",9.9E+99,AT42),FLOOR(AK42/R42,1)))</f>
-        <v/>
-      </c>
-      <c r="AM42" s="38">
-        <f>IF(AL42="","",AL42*T42)</f>
-        <v/>
-      </c>
-      <c r="AN42" s="36">
-        <f>IF(OR(AG42="",R42=0),"",MIN(IF(AT42="",9.9E+99,AT42),AK42/R42))</f>
-        <v/>
-      </c>
-      <c r="AO42" s="38">
-        <f>IF(AN42="","",AN42*T42)</f>
-        <v/>
-      </c>
-      <c r="AP42" s="40" t="n"/>
-      <c r="AQ42" s="32" t="inlineStr">
-        <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="AR42" s="41" t="n"/>
-      <c r="AS42" s="41" t="n"/>
-      <c r="AT42" s="42" t="n"/>
-      <c r="AU42" s="43">
-        <f>IF(((S42*pax_cap*load_thin*ROUND(K42*L42*revleg_thin,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_thin,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_thin*ROUND(K42*L42*revleg_thin,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_thin,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
-        <v/>
-      </c>
-      <c r="AV42" s="43">
-        <f>IF(((S42*pax_cap*load_mid*ROUND(K42*L42*revleg_mid,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_mid,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_mid*ROUND(K42*L42*revleg_mid,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_mid,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
-        <v/>
-      </c>
-      <c r="AW42" s="43">
-        <f>IF(((S42*pax_cap*load_full*ROUND(K42*L42*revleg_full,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_full,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42))&lt;=0,"",VLOOKUP(B42,country_opex,7,FALSE)/((S42*pax_cap*load_full*ROUND(K42*L42*revleg_full,0))-(((battery/range_nm)*D42*ROUND(K42*L42*revleg_full,0)*VLOOKUP(B42,country_opex,3,FALSE))+V42+W42+X42+Y42+Z42)))</f>
-        <v/>
-      </c>
-      <c r="AX42" s="44" t="inlineStr">
-        <is>
-          <t>Only existing boat is the Changi Point-&gt;Pulau Ubin bumboat: S$4/pax one-way (NParks official, T1) — budget single-class, no premium tier. No direct Marina Bay-&gt;Changi/Ubin boat (14nm long leg is greenfield). Private Ubin boat tours/charters $91-297/group = whole-boat (overclaim). Modeled premium per-seat one-way for the 14nm Marina Bay hop ~$28 (above bumboat budget, below charter).</t>
-        </is>
-      </c>
-      <c r="AY42" s="44" t="n"/>
+      <c r="A42" s="45" t="inlineStr">
+        <is>
+          <t>GROUNDED FLOOR (PUBLISHED)</t>
+        </is>
+      </c>
+      <c r="D42" s="48">
+        <f>SUM(D41:D41)</f>
+        <v/>
+      </c>
+      <c r="E42" s="46">
+        <f>SUM(E41:E41)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B43" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C43" s="30" t="inlineStr">
-        <is>
-          <t>Marina Bay Cruise Centre Singapore (MBCCS) → Punggol Point Jetty</t>
-        </is>
-      </c>
-      <c r="D43" s="31" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E43" s="26" t="n">
-        <v>59.84</v>
-      </c>
-      <c r="F43" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G43" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="33">
-        <f>60*D43/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J43" s="33">
-        <f>I43+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K43" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J43,1))</f>
-        <v/>
-      </c>
-      <c r="L43" s="34">
-        <f>ROUND(365*mech_uptime*H43,0)</f>
-        <v/>
-      </c>
-      <c r="M43" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N43" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O43" s="34">
-        <f>ROUND(K43*L43*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P43" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q43" s="36">
-        <f>pax_cap*P43</f>
-        <v/>
-      </c>
-      <c r="R43" s="34">
-        <f>Q43*O43</f>
-        <v/>
-      </c>
-      <c r="S43" s="37">
-        <f>E43*discount</f>
-        <v/>
-      </c>
-      <c r="T43" s="38">
-        <f>S43*R43</f>
-        <v/>
-      </c>
-      <c r="U43" s="38">
-        <f>(battery/range_nm)*D43*O43*VLOOKUP(B43,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V43" s="38">
-        <f>VLOOKUP(B43,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W43" s="38">
-        <f>VLOOKUP(B43,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X43" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y43" s="38">
-        <f>VLOOKUP(B43,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z43" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA43" s="38">
-        <f>U43+V43+W43+X43+Y43+Z43</f>
-        <v/>
-      </c>
-      <c r="AB43" s="38">
-        <f>VLOOKUP(B43,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC43" s="38">
-        <f>T43-AA43</f>
-        <v/>
-      </c>
-      <c r="AD43" s="35">
-        <f>IF(T43=0,"",AC43/T43)</f>
-        <v/>
-      </c>
-      <c r="AE43" s="36">
-        <f>IF(AC43&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/AC43)</f>
-        <v/>
-      </c>
-      <c r="AF43" s="33">
-        <f>((D43*O43/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D43*O43*VLOOKUP(B43,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG43" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI43" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ43" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK43" s="34">
-        <f>IF(AG43="","",AG43*AJ43)</f>
-        <v/>
-      </c>
-      <c r="AL43" s="34">
-        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AT43="",9.9E+99,AT43),FLOOR(AK43/R43,1)))</f>
-        <v/>
-      </c>
-      <c r="AM43" s="38">
-        <f>IF(AL43="","",AL43*T43)</f>
-        <v/>
-      </c>
-      <c r="AN43" s="36">
-        <f>IF(OR(AG43="",R43=0),"",MIN(IF(AT43="",9.9E+99,AT43),AK43/R43))</f>
-        <v/>
-      </c>
-      <c r="AO43" s="38">
-        <f>IF(AN43="","",AN43*T43)</f>
-        <v/>
-      </c>
-      <c r="AP43" s="40" t="n"/>
-      <c r="AQ43" s="32" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="AR43" s="41" t="n"/>
-      <c r="AS43" s="41" t="n"/>
-      <c r="AT43" s="42" t="n"/>
-      <c r="AU43" s="43">
-        <f>IF(((S43*pax_cap*load_thin*ROUND(K43*L43*revleg_thin,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_thin,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_thin*ROUND(K43*L43*revleg_thin,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_thin,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
-        <v/>
-      </c>
-      <c r="AV43" s="43">
-        <f>IF(((S43*pax_cap*load_mid*ROUND(K43*L43*revleg_mid,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_mid,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_mid*ROUND(K43*L43*revleg_mid,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_mid,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
-        <v/>
-      </c>
-      <c r="AW43" s="43">
-        <f>IF(((S43*pax_cap*load_full*ROUND(K43*L43*revleg_full,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_full,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43))&lt;=0,"",VLOOKUP(B43,country_opex,7,FALSE)/((S43*pax_cap*load_full*ROUND(K43*L43*revleg_full,0))-(((battery/range_nm)*D43*ROUND(K43*L43*revleg_full,0)*VLOOKUP(B43,country_opex,3,FALSE))+V43+W43+X43+Y43+Z43)))</f>
-        <v/>
-      </c>
-      <c r="AX43" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY43" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D43" s="51">
+        <f>SUMIF(AQ4:AQ36,"Estimated",AL4:AL36)</f>
+        <v/>
+      </c>
+      <c r="E43" s="52">
+        <f>SUMIF(AQ4:AQ36,"Estimated",AM4:AM36)</f>
+        <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B44" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C44" s="30" t="inlineStr">
-        <is>
-          <t>Marina South Pier → Pulau Ubin Jetty</t>
-        </is>
-      </c>
-      <c r="D44" s="31" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="E44" s="26" t="n">
-        <v>65.44</v>
-      </c>
-      <c r="F44" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G44" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="H44" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="33">
-        <f>60*D44/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J44" s="33">
-        <f>I44+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K44" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J44,1))</f>
-        <v/>
-      </c>
-      <c r="L44" s="34">
-        <f>ROUND(365*mech_uptime*H44,0)</f>
-        <v/>
-      </c>
-      <c r="M44" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N44" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O44" s="34">
-        <f>ROUND(K44*L44*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P44" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q44" s="36">
-        <f>pax_cap*P44</f>
-        <v/>
-      </c>
-      <c r="R44" s="34">
-        <f>Q44*O44</f>
-        <v/>
-      </c>
-      <c r="S44" s="37">
-        <f>E44*discount</f>
-        <v/>
-      </c>
-      <c r="T44" s="38">
-        <f>S44*R44</f>
-        <v/>
-      </c>
-      <c r="U44" s="38">
-        <f>(battery/range_nm)*D44*O44*VLOOKUP(B44,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V44" s="38">
-        <f>VLOOKUP(B44,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W44" s="38">
-        <f>VLOOKUP(B44,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X44" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y44" s="38">
-        <f>VLOOKUP(B44,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z44" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA44" s="38">
-        <f>U44+V44+W44+X44+Y44+Z44</f>
-        <v/>
-      </c>
-      <c r="AB44" s="38">
-        <f>VLOOKUP(B44,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC44" s="38">
-        <f>T44-AA44</f>
-        <v/>
-      </c>
-      <c r="AD44" s="35">
-        <f>IF(T44=0,"",AC44/T44)</f>
-        <v/>
-      </c>
-      <c r="AE44" s="36">
-        <f>IF(AC44&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/AC44)</f>
-        <v/>
-      </c>
-      <c r="AF44" s="33">
-        <f>((D44*O44/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D44*O44*VLOOKUP(B44,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG44" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="AI44" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
-      <c r="AJ44" s="39" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AK44" s="34">
-        <f>IF(AG44="","",AG44*AJ44)</f>
-        <v/>
-      </c>
-      <c r="AL44" s="34">
-        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AT44="",9.9E+99,AT44),FLOOR(AK44/R44,1)))</f>
-        <v/>
-      </c>
-      <c r="AM44" s="38">
-        <f>IF(AL44="","",AL44*T44)</f>
-        <v/>
-      </c>
-      <c r="AN44" s="36">
-        <f>IF(OR(AG44="",R44=0),"",MIN(IF(AT44="",9.9E+99,AT44),AK44/R44))</f>
-        <v/>
-      </c>
-      <c r="AO44" s="38">
-        <f>IF(AN44="","",AN44*T44)</f>
-        <v/>
-      </c>
-      <c r="AP44" s="40" t="n"/>
-      <c r="AQ44" s="32" t="inlineStr">
-        <is>
-          <t>Estimated</t>
-        </is>
-      </c>
-      <c r="AR44" s="41" t="n"/>
-      <c r="AS44" s="41" t="n"/>
-      <c r="AT44" s="42" t="n"/>
-      <c r="AU44" s="43">
-        <f>IF(((S44*pax_cap*load_thin*ROUND(K44*L44*revleg_thin,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_thin,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_thin*ROUND(K44*L44*revleg_thin,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_thin,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
-        <v/>
-      </c>
-      <c r="AV44" s="43">
-        <f>IF(((S44*pax_cap*load_mid*ROUND(K44*L44*revleg_mid,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_mid,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_mid*ROUND(K44*L44*revleg_mid,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_mid,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
-        <v/>
-      </c>
-      <c r="AW44" s="43">
-        <f>IF(((S44*pax_cap*load_full*ROUND(K44*L44*revleg_full,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_full,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44))&lt;=0,"",VLOOKUP(B44,country_opex,7,FALSE)/((S44*pax_cap*load_full*ROUND(K44*L44*revleg_full,0))-(((battery/range_nm)*D44*ROUND(K44*L44*revleg_full,0)*VLOOKUP(B44,country_opex,3,FALSE))+V44+W44+X44+Y44+Z44)))</f>
-        <v/>
-      </c>
-      <c r="AX44" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
-        </is>
-      </c>
-      <c r="AY44" s="44" t="inlineStr">
-        <is>
-          <t>economics_by_route_id.json</t>
+      <c r="A44" s="53" t="inlineStr">
+        <is>
+          <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
+        </is>
+      </c>
+      <c r="C44" s="54" t="inlineStr">
+        <is>
+          <t>Karimunjawa Archipelago → Jakarta (223.5nm)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B45" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C45" s="30" t="inlineStr">
-        <is>
-          <t>Singapore → Bintan (Lagoi resort zone)</t>
-        </is>
-      </c>
-      <c r="D45" s="31" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E45" s="26" t="n">
-        <v>69</v>
-      </c>
-      <c r="F45" s="32" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="G45" s="32" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="H45" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="33">
-        <f>60*D45/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J45" s="33">
-        <f>I45+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K45" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J45,1))</f>
-        <v/>
-      </c>
-      <c r="L45" s="34">
-        <f>ROUND(365*mech_uptime*H45,0)</f>
-        <v/>
-      </c>
-      <c r="M45" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N45" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O45" s="34">
-        <f>ROUND(K45*L45*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P45" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q45" s="36">
-        <f>pax_cap*P45</f>
-        <v/>
-      </c>
-      <c r="R45" s="34">
-        <f>Q45*O45</f>
-        <v/>
-      </c>
-      <c r="S45" s="37">
-        <f>E45*discount</f>
-        <v/>
-      </c>
-      <c r="T45" s="38">
-        <f>S45*R45</f>
-        <v/>
-      </c>
-      <c r="U45" s="38">
-        <f>(battery/range_nm)*D45*O45*VLOOKUP(B45,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V45" s="38">
-        <f>VLOOKUP(B45,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W45" s="38">
-        <f>VLOOKUP(B45,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X45" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y45" s="38">
-        <f>VLOOKUP(B45,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z45" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA45" s="38">
-        <f>U45+V45+W45+X45+Y45+Z45</f>
-        <v/>
-      </c>
-      <c r="AB45" s="38">
-        <f>VLOOKUP(B45,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC45" s="38">
-        <f>T45-AA45</f>
-        <v/>
-      </c>
-      <c r="AD45" s="35">
-        <f>IF(T45=0,"",AC45/T45)</f>
-        <v/>
-      </c>
-      <c r="AE45" s="36">
-        <f>IF(AC45&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/AC45)</f>
-        <v/>
-      </c>
-      <c r="AF45" s="33">
-        <f>((D45*O45/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D45*O45*VLOOKUP(B45,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG45" s="31" t="n">
-        <v>150000</v>
-      </c>
-      <c r="AH45" s="32" t="n"/>
-      <c r="AI45" s="32" t="n"/>
-      <c r="AJ45" s="39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK45" s="34">
-        <f>IF(AG45="","",AG45*AJ45)</f>
-        <v/>
-      </c>
-      <c r="AL45" s="34">
-        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AT45="",9.9E+99,AT45),FLOOR(AK45/R45,1)))</f>
-        <v/>
-      </c>
-      <c r="AM45" s="38">
-        <f>IF(AL45="","",AL45*T45)</f>
-        <v/>
-      </c>
-      <c r="AN45" s="36">
-        <f>IF(OR(AG45="",R45=0),"",MIN(IF(AT45="",9.9E+99,AT45),AK45/R45))</f>
-        <v/>
-      </c>
-      <c r="AO45" s="38">
-        <f>IF(AN45="","",AN45*T45)</f>
-        <v/>
-      </c>
-      <c r="AP45" s="40" t="n"/>
-      <c r="AQ45" s="32" t="inlineStr">
-        <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="AR45" s="41" t="n"/>
-      <c r="AS45" s="41" t="n"/>
-      <c r="AT45" s="42" t="n"/>
-      <c r="AU45" s="43">
-        <f>IF(((S45*pax_cap*load_thin*ROUND(K45*L45*revleg_thin,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_thin,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_thin*ROUND(K45*L45*revleg_thin,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_thin,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
-        <v/>
-      </c>
-      <c r="AV45" s="43">
-        <f>IF(((S45*pax_cap*load_mid*ROUND(K45*L45*revleg_mid,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_mid,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_mid*ROUND(K45*L45*revleg_mid,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_mid,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
-        <v/>
-      </c>
-      <c r="AW45" s="43">
-        <f>IF(((S45*pax_cap*load_full*ROUND(K45*L45*revleg_full,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_full,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45))&lt;=0,"",VLOOKUP(B45,country_opex,7,FALSE)/((S45*pax_cap*load_full*ROUND(K45*L45*revleg_full,0))-(((battery/range_nm)*D45*ROUND(K45*L45*revleg_full,0)*VLOOKUP(B45,country_opex,3,FALSE))+V45+W45+X45+Y45+Z45)))</f>
-        <v/>
-      </c>
-      <c r="AX45" s="44" t="inlineStr">
-        <is>
-          <t>Bintan Resort Ferries (BRF, official) Tanah Merah↔Bandar Bentan Telani (Lagoi resort zone), fares eff. 12 Mar 2026: Economy one-way SGD62 adult; EMERALD CLASS one-way SGD89 adult (premium per-seat tier, incl levies). 3rd-party budget listings from SGD53. Charter = 180-270 pax whole vessel (excluded, R1).</t>
-        </is>
-      </c>
-      <c r="AY45" s="44" t="n"/>
+      <c r="C45" s="54" t="inlineStr">
+        <is>
+          <t>Komodo / Labuan Bajo → Sumba (Nihi) (90nm)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B46" s="29" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C46" s="30" t="inlineStr">
-        <is>
-          <t>Singapore → Desaru Coast / Johor</t>
-        </is>
-      </c>
-      <c r="D46" s="31" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E46" s="26" t="n">
-        <v>47</v>
-      </c>
-      <c r="F46" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G46" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="33">
-        <f>60*D46/cruise_kt</f>
-        <v/>
-      </c>
-      <c r="J46" s="33">
-        <f>I46+turn_min+dwell_min</f>
-        <v/>
-      </c>
-      <c r="K46" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J46,1))</f>
-        <v/>
-      </c>
-      <c r="L46" s="34">
-        <f>ROUND(365*mech_uptime*H46,0)</f>
-        <v/>
-      </c>
-      <c r="M46" s="35">
-        <f>mech_uptime</f>
-        <v/>
-      </c>
-      <c r="N46" s="35">
-        <f>revleg_sel</f>
-        <v/>
-      </c>
-      <c r="O46" s="34">
-        <f>ROUND(K46*L46*revleg_sel,0)</f>
-        <v/>
-      </c>
-      <c r="P46" s="36">
-        <f>load_sel</f>
-        <v/>
-      </c>
-      <c r="Q46" s="36">
-        <f>pax_cap*P46</f>
-        <v/>
-      </c>
-      <c r="R46" s="34">
-        <f>Q46*O46</f>
-        <v/>
-      </c>
-      <c r="S46" s="37">
-        <f>E46*discount</f>
-        <v/>
-      </c>
-      <c r="T46" s="38">
-        <f>S46*R46</f>
-        <v/>
-      </c>
-      <c r="U46" s="38">
-        <f>(battery/range_nm)*D46*O46*VLOOKUP(B46,country_opex,3,FALSE)</f>
-        <v/>
-      </c>
-      <c r="V46" s="38">
-        <f>VLOOKUP(B46,country_opex,2,FALSE)*crew_factor</f>
-        <v/>
-      </c>
-      <c r="W46" s="38">
-        <f>VLOOKUP(B46,country_opex,5,FALSE)</f>
-        <v/>
-      </c>
-      <c r="X46" s="38">
-        <f>maint</f>
-        <v/>
-      </c>
-      <c r="Y46" s="38">
-        <f>VLOOKUP(B46,country_opex,7,FALSE)*ins_pct</f>
-        <v/>
-      </c>
-      <c r="Z46" s="38">
-        <f>charge_berth</f>
-        <v/>
-      </c>
-      <c r="AA46" s="38">
-        <f>U46+V46+W46+X46+Y46+Z46</f>
-        <v/>
-      </c>
-      <c r="AB46" s="38">
-        <f>VLOOKUP(B46,country_opex,7,FALSE)/dep_years</f>
-        <v/>
-      </c>
-      <c r="AC46" s="38">
-        <f>T46-AA46</f>
-        <v/>
-      </c>
-      <c r="AD46" s="35">
-        <f>IF(T46=0,"",AC46/T46)</f>
-        <v/>
-      </c>
-      <c r="AE46" s="36">
-        <f>IF(AC46&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/AC46)</f>
-        <v/>
-      </c>
-      <c r="AF46" s="33">
-        <f>((D46*O46/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D46*O46*VLOOKUP(B46,country_opex,4,FALSE))/1000</f>
-        <v/>
-      </c>
-      <c r="AG46" s="31" t="n">
-        <v>22500</v>
-      </c>
-      <c r="AH46" s="32" t="n"/>
-      <c r="AI46" s="32" t="n"/>
-      <c r="AJ46" s="39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK46" s="34">
-        <f>IF(AG46="","",AG46*AJ46)</f>
-        <v/>
-      </c>
-      <c r="AL46" s="34">
-        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AT46="",9.9E+99,AT46),FLOOR(AK46/R46,1)))</f>
-        <v/>
-      </c>
-      <c r="AM46" s="38">
-        <f>IF(AL46="","",AL46*T46)</f>
-        <v/>
-      </c>
-      <c r="AN46" s="36">
-        <f>IF(OR(AG46="",R46=0),"",MIN(IF(AT46="",9.9E+99,AT46),AK46/R46))</f>
-        <v/>
-      </c>
-      <c r="AO46" s="38">
-        <f>IF(AN46="","",AN46*T46)</f>
-        <v/>
-      </c>
-      <c r="AP46" s="40" t="n"/>
-      <c r="AQ46" s="32" t="inlineStr">
-        <is>
-          <t>Grounded</t>
-        </is>
-      </c>
-      <c r="AR46" s="41" t="n"/>
-      <c r="AS46" s="41" t="n"/>
-      <c r="AT46" s="42" t="n"/>
-      <c r="AU46" s="43">
-        <f>IF(((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_thin*ROUND(K46*L46*revleg_thin,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_thin,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
-        <v/>
-      </c>
-      <c r="AV46" s="43">
-        <f>IF(((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_mid*ROUND(K46*L46*revleg_mid,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_mid,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
-        <v/>
-      </c>
-      <c r="AW46" s="43">
-        <f>IF(((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46))&lt;=0,"",VLOOKUP(B46,country_opex,7,FALSE)/((S46*pax_cap*load_full*ROUND(K46*L46*revleg_full,0))-(((battery/range_nm)*D46*ROUND(K46*L46*revleg_full,0)*VLOOKUP(B46,country_opex,3,FALSE))+V46+W46+X46+Y46+Z46)))</f>
-        <v/>
-      </c>
-      <c r="AX46" s="44" t="inlineStr">
-        <is>
-          <t>Tanah Merah↔Desaru Coast ferry (BatamFast). Fare ladder: promo/budget SGD26 (busonlineticket); standard one-way SGD50 (Traveloka); full published one-way ~SGD58-70 (redBus 'from SGD70', instarem breakdown base SGD68). Single operator, essentially single-class fast ferry serving Desaru Coast luxury resorts (One&amp;Only, Anantara, Westin). Whole-vessel charter excluded (150-338 pax ferries).</t>
-        </is>
-      </c>
-      <c r="AY46" s="44" t="n"/>
+      <c r="C46" s="54" t="inlineStr">
+        <is>
+          <t>Lombok → Komodo / Labuan Bajo (237nm)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="45" t="inlineStr">
-        <is>
-          <t>TOTAL / median</t>
-        </is>
-      </c>
-      <c r="T47" s="46">
-        <f>SUM(T4:T46)</f>
-        <v/>
-      </c>
-      <c r="AC47" s="46">
-        <f>SUM(AC4:AC46)</f>
-        <v/>
-      </c>
-      <c r="AD47" s="47">
-        <f>IF(T47=0,"",AC47/T47)</f>
-        <v/>
-      </c>
-      <c r="AL47" s="48">
-        <f>SUM(AL4:AL46)</f>
-        <v/>
-      </c>
-      <c r="AM47" s="46">
-        <f>SUM(AM4:AM46)</f>
-        <v/>
+      <c r="C47" s="54" t="inlineStr">
+        <is>
+          <t>Raja Ampat → Misool (114.6nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="54" t="inlineStr">
+        <is>
+          <t>Komodo / Labuan Bajo / Flores / Sumba → Sumba (82.9nm)</t>
+        </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Fleet basis</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>Raw vessels (sum)</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>Fleet (rounded once)</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>Market rev/yr (raw sum)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>Gojek</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>network_sum / ceil</t>
-        </is>
-      </c>
-      <c r="C51" s="23">
-        <f>SUMIFS(AN4:AN46,A4:A46,"Gojek",AP4:AP46,"=",AQ4:AQ46,"Grounded")</f>
-        <v/>
-      </c>
-      <c r="D51" s="49">
-        <f>IF(C51=0,0,CEILING(C51,1))</f>
-        <v/>
-      </c>
-      <c r="E51" s="50">
-        <f>SUMIFS(AO4:AO46,A4:A46,"Gojek",AP4:AP46,"=",AQ4:AQ46,"Grounded")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="45" t="inlineStr">
-        <is>
-          <t>GROUNDED FLOOR (PUBLISHED)</t>
-        </is>
-      </c>
-      <c r="D52" s="48">
-        <f>SUM(D51:D51)</f>
-        <v/>
-      </c>
-      <c r="E52" s="46">
-        <f>SUM(E51:E51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
-        </is>
-      </c>
-      <c r="D53" s="51">
-        <f>SUMIF(AQ4:AQ46,"Estimated",AL4:AL46)</f>
-        <v/>
-      </c>
-      <c r="E53" s="52">
-        <f>SUMIF(AQ4:AQ46,"Estimated",AM4:AM46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="53" t="inlineStr">
-        <is>
-          <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
-        </is>
-      </c>
-      <c r="C54" s="54" t="inlineStr">
-        <is>
-          <t>Karimunjawa Archipelago → Jakarta (223.5nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" s="54" t="inlineStr">
-        <is>
-          <t>Komodo / Labuan Bajo → Sumba (Nihi) (90nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" s="54" t="inlineStr">
-        <is>
-          <t>Lombok → Komodo / Labuan Bajo (237nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" s="54" t="inlineStr">
-        <is>
-          <t>Raja Ampat → Misool (114.6nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" s="54" t="inlineStr">
-        <is>
-          <t>Komodo / Labuan Bajo / Flores / Sumba → Sumba (82.9nm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" s="54" t="inlineStr">
+      <c r="C49" s="54" t="inlineStr">
         <is>
           <t>Marina Labuan Bajo → Maumere Port (Lorenz Say) — Kelimutu access (153.3nm)</t>
         </is>
@@ -10942,7 +8964,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11112,11 +9134,11 @@
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>0.1327</v>
+        <v>0.1</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>New-entrant ~13% share of today's pool (= the published floor).</t>
+          <t>New-entrant ~10% share of today's pool (= the published floor).</t>
         </is>
       </c>
     </row>
@@ -11189,7 +9211,7 @@
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>SOM full network (~13% capture, today, +greenfield)</t>
+          <t>SOM full network (~10% capture, today, +greenfield)</t>
         </is>
       </c>
       <c r="B18" s="50">
@@ -11206,7 +9228,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Floor posture (~13% captive capture, today's demand) extended across the whole mapped network.</t>
+          <t>Floor posture (~10% captive capture, today's demand) extended across the whole mapped network.</t>
         </is>
       </c>
     </row>
